--- a/driver_forms/021_female_cab_driver_survey--driver_forms.xlsx
+++ b/driver_forms/021_female_cab_driver_survey--driver_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-5_years',_'value':_'5_years'}</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-5 Years', 'value': '5 years'}</t>
+          <t>1-5 Years</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'5-10_years',_'value':_'10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '5-10 Years', 'value': '10 years'}</t>
+          <t>5-10 Years</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'more_than_10_years',_'value':_'more_than_10_years'}</t>
+          <t>more_than_10_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'More than 10 Years', 'value': 'more than 10 years'}</t>
+          <t>More than 10 Years</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_2_hours',_'value':_'less_than_2'}</t>
+          <t>less_than_2_hours</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 2 hours', 'value': 'less than 2'}</t>
+          <t>Less than 2 hours</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2-10_hours',_'value':_'2-10_hours'}</t>
+          <t>2-10_hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2-10 hours', 'value': '2-10 hours'}</t>
+          <t>2-10 hours</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'more_than_10_hours',_'value':_'more_than_10_hours'}</t>
+          <t>more_than_10_hours</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'More than 10 hours', 'value': 'more than 10 hours'}</t>
+          <t>More than 10 hours</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sedan',_'value':_'sedan'}</t>
+          <t>sedan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sedan', 'value': 'sedan'}</t>
+          <t>Sedan</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'suv',_'value':_'suv'}</t>
+          <t>suv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'SUV', 'value': 'suv'}</t>
+          <t>SUV</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'truck',_'value':_'truck'}</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Truck', 'value': 'truck'}</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'motorcycle',_'value':_'motorcycle'}</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Motorcycle', 'value': 'motorcycle'}</t>
+          <t>Motorcycle</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male', 'value': 'male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female', 'value': 'female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
